--- a/data_transform/quantidade_processos.xlsx
+++ b/data_transform/quantidade_processos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,17 +417,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>nucleo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>quantidade</t>
         </is>
@@ -448,37 +436,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>1ª CC</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>703</v>
+        <v>713</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1ª CC</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>476</v>
+        <v>692</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,13 +475,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>466</v>
+        <v>487</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -502,13 +490,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>438</v>
+        <v>454</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -517,133 +505,133 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>347</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6ª CCJ</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>255</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>1ª CCJ</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>251</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5ª CCJ</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>239</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1ª CCJ</t>
+          <t>6ª CCJ</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2ª CCJ</t>
+          <t>4ª CCJ</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>5ª CCJ</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>226</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>3ª CCJ</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -652,7 +640,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data_transform/quantidade_processos.xlsx
+++ b/data_transform/quantidade_processos.xlsx
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>713</v>
+        <v>758</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -460,43 +460,43 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>692</v>
+        <v>742</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>3ª CC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>487</v>
+        <v>424</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>454</v>
+        <v>397</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -505,28 +505,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2ª CCJ</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>270</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -535,28 +535,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>264</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>253</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -565,43 +565,43 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>5ª CCJ</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5ª CCJ</t>
+          <t>4ª CCJ</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -616,7 +616,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data_transform/quantidade_processos.xlsx
+++ b/data_transform/quantidade_processos.xlsx
@@ -436,37 +436,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1ª CC</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>758</v>
+        <v>774</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>1ª CC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>742</v>
+        <v>754</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -481,7 +481,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -490,33 +490,33 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>397</v>
+        <v>407</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>307</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -526,7 +526,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -535,13 +535,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>282</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -550,13 +550,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>207</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -610,13 +610,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/data_transform/quantidade_processos.xlsx
+++ b/data_transform/quantidade_processos.xlsx
@@ -436,37 +436,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>1ª CC</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>774</v>
+        <v>847</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1ª CC</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>754</v>
+        <v>780</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -475,13 +475,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>424</v>
+        <v>462</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -490,148 +490,148 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>407</v>
+        <v>455</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>1ª CCJ</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>314</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>301</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1ª CCJ</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>289</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2ª CCJ</t>
+          <t>5ª CCJ</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>273</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6ª CCJ</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>240</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5ª CCJ</t>
+          <t>6ª CCJ</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>227</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>3ª CCJ</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>4ª CCJ</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data_transform/quantidade_processos.xlsx
+++ b/data_transform/quantidade_processos.xlsx
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>847</v>
+        <v>934</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>780</v>
+        <v>849</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -481,97 +481,97 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>1ª CCJ</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1ª CCJ</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>325</v>
+        <v>452</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5ª CCJ</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2ª CCJ</t>
+          <t>5ª CCJ</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>255</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -580,43 +580,43 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>4ª CCJ</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>3ª CCJ</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>207</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>205</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/data_transform/quantidade_processos.xlsx
+++ b/data_transform/quantidade_processos.xlsx
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>934</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -460,43 +460,43 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>1ª CCJ</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>462</v>
+        <v>519</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1ª CCJ</t>
+          <t>3ª CC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>459</v>
+        <v>376</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>452</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -520,103 +520,103 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>290</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>5ª CCJ</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>272</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4ª CC</t>
+          <t>4ª CCJ</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>269</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5ª CCJ</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6ª CCJ</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>221</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>3ª CCJ</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>220</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>6ª CCJ</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>219</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>215</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/data_transform/quantidade_processos.xlsx
+++ b/data_transform/quantidade_processos.xlsx
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1037</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>890</v>
+        <v>886</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -475,13 +475,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>519</v>
+        <v>566</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -490,28 +490,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>376</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>5ª CCJ</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>332</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -520,28 +520,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>320</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5ª CCJ</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>290</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -550,58 +550,58 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4ª CC</t>
+          <t>3ª CCJ</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>258</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -610,13 +610,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>194</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/data_transform/quantidade_processos.xlsx
+++ b/data_transform/quantidade_processos.xlsx
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1068</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>886</v>
+        <v>976</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -475,13 +475,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>566</v>
+        <v>611</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>341</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>320</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -520,13 +520,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -535,13 +535,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>302</v>
+        <v>285</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -550,13 +550,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>263</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -601,7 +601,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -610,13 +610,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>178</v>
+        <v>197</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/data_transform/quantidade_processos.xlsx
+++ b/data_transform/quantidade_processos.xlsx
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -445,43 +445,43 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1037</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>1ª CCJ</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>976</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1ª CCJ</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>611</v>
+        <v>674</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -490,148 +490,148 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>321</v>
+        <v>515</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5ª CCJ</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2ª CCJ</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>298</v>
+        <v>373</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4ª CC</t>
+          <t>5ª CCJ</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>285</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>269</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>289</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>231</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>4ª CCJ</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>208</v>
+        <v>244</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6ª CCJ</t>
+          <t>3ª CCJ</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>197</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>6ª CCJ</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/data_transform/quantidade_processos.xlsx
+++ b/data_transform/quantidade_processos.xlsx
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1315</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -460,88 +460,88 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1179</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>3ª CC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>674</v>
+        <v>649</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3ª CC</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>533</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2ª CCJ</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>373</v>
+        <v>343</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -550,43 +550,43 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>292</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>6ª CCJ</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>289</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>3ª CCJ</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>282</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -595,43 +595,43 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6ª CCJ</t>
+          <t>5ª CCJ</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/data_transform/quantidade_processos.xlsx
+++ b/data_transform/quantidade_processos.xlsx
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1687</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1374</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -475,13 +475,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>649</v>
+        <v>674</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>533</v>
+        <v>555</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>415</v>
+        <v>457</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -520,118 +520,118 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>343</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>6ª CCJ</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>254</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6ª CCJ</t>
+          <t>5ª CCJ</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>253</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>4ª CCJ</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>239</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>3ª CCJ</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5ª CCJ</t>
+          <t>2ª CC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>223</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/data_transform/quantidade_processos.xlsx
+++ b/data_transform/quantidade_processos.xlsx
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1509</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1438</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -475,13 +475,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>674</v>
+        <v>685</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -520,13 +520,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>301</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -535,28 +535,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>4ª CCJ</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>287</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -565,28 +565,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>259</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>252</v>
+        <v>244</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -610,13 +610,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>122</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/data_transform/quantidade_processos.xlsx
+++ b/data_transform/quantidade_processos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -445,28 +445,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1512</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1ª CCJ</t>
+          <t>7ª CCJ</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1435</v>
+        <v>810</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -475,88 +475,88 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>685</v>
+        <v>714</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2ª CCJ</t>
+          <t>1ª CCJ</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>551</v>
+        <v>580</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>2ª CCJ</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>458</v>
+        <v>575</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5ª CC</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>318</v>
+        <v>495</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6ª CCJ</t>
+          <t>5ª CC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>300</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>6ª CCJ</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>272</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -565,82 +565,97 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>264</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>4ª CCJ</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>246</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4ª CC</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>244</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>225</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2ª CC</t>
+          <t>3ª CCJ</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>93</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>2ª CC</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>PARTIDOR</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>37</v>
+      <c r="C16" t="n">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/data_transform/quantidade_processos.xlsx
+++ b/data_transform/quantidade_processos.xlsx
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1485</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>810</v>
+        <v>799</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -475,13 +475,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>714</v>
+        <v>703</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -496,7 +496,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -520,13 +520,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -535,13 +535,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -550,13 +550,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -565,43 +565,43 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>4ª CCJ</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -610,13 +610,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>252</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>120</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">

--- a/data_transform/quantidade_processos.xlsx
+++ b/data_transform/quantidade_processos.xlsx
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1487</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>799</v>
+        <v>825</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -475,13 +475,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>703</v>
+        <v>722</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>580</v>
+        <v>573</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>578</v>
+        <v>570</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -520,13 +520,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>496</v>
+        <v>539</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -535,13 +535,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -550,43 +550,43 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>330</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5ª CCJ</t>
+          <t>4ª CC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>276</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>5ª CCJ</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -595,43 +595,43 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4ª CC</t>
+          <t>3ª CCJ</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>272</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>218</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/data_transform/quantidade_processos.xlsx
+++ b/data_transform/quantidade_processos.xlsx
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1461</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>825</v>
+        <v>848</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -475,28 +475,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>722</v>
+        <v>790</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1ª CCJ</t>
+          <t>6ª CC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>573</v>
+        <v>605</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -505,28 +505,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>570</v>
+        <v>585</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6ª CC</t>
+          <t>1ª CCJ</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>539</v>
+        <v>577</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -535,13 +535,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>360</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -550,13 +550,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>344</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -565,63 +565,63 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>290</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5ª CCJ</t>
+          <t>4ª CCJ</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4ª CCJ</t>
+          <t>5ª CCJ</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3ª CCJ</t>
+          <t>7ª CC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>232</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7ª CC</t>
+          <t>3ª CCJ</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -631,7 +631,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>128</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
